--- a/請款流程_已完成開發規則.xlsx
+++ b/請款流程_已完成開發規則.xlsx
@@ -7,15 +7,16 @@
     <workbookView xWindow="840" yWindow="825" windowWidth="27495" windowHeight="11415"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表2" sheetId="1" r:id="rId1"/>
+    <sheet name="欄位" sheetId="1" r:id="rId1"/>
     <sheet name="簽核流程規則" sheetId="2" r:id="rId2"/>
+    <sheet name="結果檔案" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="191">
   <si>
     <t>請款單號</t>
   </si>
@@ -1133,16 +1134,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1172,7 +1173,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="/xl/media/image1.png"/>
+        <xdr:cNvPr id="2" name="/xl/media/image1.png"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2028,14 +2029,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5"/>
@@ -2046,14 +2047,14 @@
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="34" t="s">
@@ -2124,14 +2125,14 @@
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="34" t="s">
@@ -2254,14 +2255,14 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="10" t="s">
@@ -2368,14 +2369,14 @@
       <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" ht="24" customHeight="1">
-      <c r="A25" s="50" t="s">
+      <c r="A25" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="20" t="s">
@@ -2562,14 +2563,14 @@
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" ht="24" customHeight="1">
-      <c r="A37" s="50" t="s">
+      <c r="A37" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="20" t="s">
@@ -2672,14 +2673,14 @@
       <c r="F43" s="5"/>
     </row>
     <row r="44" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A44" s="51" t="s">
+      <c r="A44" s="49" t="s">
         <v>176</v>
       </c>
-      <c r="B44" s="51"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="51"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="5"/>
@@ -2690,14 +2691,14 @@
       <c r="F45" s="5"/>
     </row>
     <row r="46" spans="1:6" ht="24" customHeight="1">
-      <c r="A46" s="50" t="s">
+      <c r="A46" s="48" t="s">
         <v>177</v>
       </c>
-      <c r="B46" s="50"/>
-      <c r="C46" s="50"/>
-      <c r="D46" s="50"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="50"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="48"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="20" t="s">
@@ -2768,14 +2769,14 @@
       <c r="F50" s="5"/>
     </row>
     <row r="51" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A51" s="51" t="s">
+      <c r="A51" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="B51" s="51"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2792,4 +2793,41 @@
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+    </row>
+    <row r="2" spans="1:4" ht="33">
+      <c r="A2" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>